--- a/Hoadon/HD2026/HDVao/3/3502551856_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/3/3502551856_HDDienTuDaCapMa.xlsx
@@ -255,17 +255,17 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Địa chỉ người bán</t>
+          <t>MST người mua/MST người nhận hàng</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>MST người mua/MST người nhận hàng</t>
+          <t>Tên người mua/Tên người nhận hàng</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Tên người mua/Tên người nhận hàng</t>
+          <t>Địa chỉ người mua</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -348,19 +348,19 @@
           <t>CÔNG TY TNHH THẢO KHÁNH TÂM</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Số 985 Quốc Lộ 1A, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>3502551856</t>
         </is>
       </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Số 88 Nguyễn Tri Phương, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
@@ -431,19 +431,19 @@
           <t>CÔNG TY TNHH THẢO KHÁNH TÂM</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Số 985 Quốc Lộ 1A, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>3502551856</t>
         </is>
       </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Số 88 Nguyễn Tri Phương, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
@@ -514,19 +514,19 @@
           <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>3502551856</t>
         </is>
       </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Số 88 Nguyễn Tri Phương, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
